--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_2502.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_2502.xlsx
@@ -2266,6 +2266,9 @@
       <c r="E32" t="n">
         <v>0.297</v>
       </c>
+      <c r="F32" t="n">
+        <v>0.7</v>
+      </c>
       <c r="G32" t="n">
         <v>0.5625</v>
       </c>
@@ -2284,12 +2287,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-06-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-06-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-06-08 dims are NOT assumed; confirm before modelling | Brennan CAD record 2502-06-08-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-06-08 dims are NOT assumed; confirm before modelling | Brennan CAD record 2502-06-08-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2323,6 +2326,9 @@
       <c r="E33" t="n">
         <v>0.391</v>
       </c>
+      <c r="F33" t="n">
+        <v>0.43</v>
+      </c>
       <c r="G33" t="n">
         <v>0.75</v>
       </c>
@@ -2341,12 +2347,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-08-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-08-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-08-04 dims are NOT assumed; confirm before modelling | Brennan CAD record 2502-08-04-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-08-04 dims are NOT assumed; confirm before modelling | Brennan CAD record 2502-08-04-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2380,6 +2386,9 @@
       <c r="E34" t="n">
         <v>0.609</v>
       </c>
+      <c r="F34" t="n">
+        <v>0.7</v>
+      </c>
       <c r="G34" t="n">
         <v>1.0625</v>
       </c>
@@ -2398,12 +2407,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-12-08 dims are NOT assumed; confirm before modelling | Brennan CAD record 2502-12-08-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-12-08 dims are NOT assumed; confirm before modelling | Brennan CAD record 2502-12-08-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2437,6 +2446,9 @@
       <c r="E35" t="n">
         <v>0.844</v>
       </c>
+      <c r="F35" t="n">
+        <v>1.48</v>
+      </c>
       <c r="G35" t="n">
         <v>1.3125</v>
       </c>
@@ -2455,12 +2467,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-16-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-16-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-16-20 dims are NOT assumed; confirm before modelling | Brennan CAD record 2502-16-20-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-16-20 dims are NOT assumed; confirm before modelling | Brennan CAD record 2502-16-20-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2485,6 +2497,9 @@
           <t>2502-20-16-FG</t>
         </is>
       </c>
+      <c r="F36" t="n">
+        <v>1.14</v>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>2502-20-16-FG</t>
@@ -2497,12 +2512,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2531,6 +2546,9 @@
       <c r="E37" t="n">
         <v>1.312</v>
       </c>
+      <c r="F37" t="n">
+        <v>1.72</v>
+      </c>
       <c r="G37" t="n">
         <v>1.875</v>
       </c>
@@ -2549,12 +2567,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2502-24-24 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 2502-24-24-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2502-24-24 dims are NOT assumed; confirm before modelling | Brennan CAD record 2502-24-24-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2588,6 +2606,9 @@
       <c r="E38" t="n">
         <v>1.781</v>
       </c>
+      <c r="F38" t="n">
+        <v>2.2</v>
+      </c>
       <c r="G38" t="n">
         <v>2.5</v>
       </c>
@@ -2606,12 +2627,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, M1@DRIVE, N1@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 2502-32-32-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 2502-32-32-FG (PARTcommunity / CADENAS, D@BORE=B1D, M1@DRIVE=M, N1@DRIVE=L, THDMAJ_A@DRIVE=A2THD, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
